--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -560,7 +560,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -575,10 +575,10 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -621,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -8,13 +8,15 @@
   <sheets>
     <sheet name="strength_of_majority" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="perc_author_opinion_unanimous" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="solo_dissents" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="coalition_sizesjustice" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="perc_opinions_unanimous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="solo_dissents" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t xml:space="preserve">justice</t>
   </si>
@@ -68,6 +70,27 @@
   </si>
   <si>
     <t xml:space="preserve">percent_unanimous</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_opinions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maj_9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maj_8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maj_7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maj_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maj_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean_coalition</t>
   </si>
   <si>
     <t xml:space="preserve">solo_dissents</t>
@@ -534,10 +557,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -768,6 +791,368 @@
       <c r="B1" t="s">
         <v>18</v>
       </c>
+      <c r="C1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.33</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -609,13 +609,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -627,7 +627,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>7.33333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -635,10 +635,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="9">
@@ -762,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="10">
@@ -838,19 +838,19 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -859,33 +859,33 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>9</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -971,11 +971,11 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
@@ -989,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="9">
@@ -997,10 +997,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1073,18 +1073,18 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -1116,7 +1116,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9">
@@ -1124,7 +1124,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -479,10 +479,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>7.66666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -505,10 +505,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -531,11 +531,11 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="6">
@@ -557,10 +557,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -661,11 +661,11 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8.5</v>
+        <v>8.66666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -714,7 +714,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="4">
@@ -730,7 +730,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
@@ -770,7 +770,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>
@@ -841,10 +841,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
     </row>
     <row r="4">
@@ -867,10 +867,10 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -893,11 +893,11 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6">
@@ -919,10 +919,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1023,11 +1023,11 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8.5</v>
+        <v>8.67</v>
       </c>
     </row>
   </sheetData>
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -1132,7 +1132,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -453,11 +453,11 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
         <v>2</v>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
@@ -471,7 +471,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>8.33333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -479,10 +479,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.66666666666667</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -531,13 +531,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -549,7 +549,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="6">
@@ -583,10 +583,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
@@ -635,13 +635,13 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -653,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="10">
@@ -661,11 +661,11 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8.66666666666667</v>
+        <v>8.75</v>
       </c>
     </row>
   </sheetData>
@@ -706,7 +706,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="3">
@@ -714,7 +714,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -730,7 +730,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -762,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -770,7 +770,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -815,11 +815,11 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
         <v>2</v>
       </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="3">
@@ -841,10 +841,10 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -893,13 +893,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6">
@@ -945,10 +945,10 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="8">
@@ -997,13 +997,13 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="10">
@@ -1023,11 +1023,11 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" t="n">
         <v>3</v>
       </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
@@ -1041,7 +1041,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>8.67</v>
+        <v>8.75</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1068,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -1092,7 +1092,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -1108,7 +1108,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -1124,7 +1124,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -1132,7 +1132,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -453,11 +453,11 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
@@ -465,13 +465,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>8.33333333333333</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
@@ -479,16 +479,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -497,7 +497,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>7.83333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -583,13 +583,13 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -601,7 +601,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -609,7 +609,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -618,16 +618,16 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>7.33333333333333</v>
+        <v>6.83333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -635,7 +635,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -644,7 +644,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>7.25</v>
+        <v>7.16666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -706,7 +706,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -714,7 +714,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="4">
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="8">
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="9">
@@ -762,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="10">
@@ -815,11 +815,11 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
@@ -827,13 +827,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>8.33</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
@@ -841,16 +841,16 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -945,13 +945,13 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -963,7 +963,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -971,7 +971,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
@@ -980,16 +980,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -1006,7 +1006,7 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>7.25</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="10">
@@ -1068,7 +1068,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1108,7 +1108,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -1116,7 +1116,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -1124,7 +1124,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -508,7 +508,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -520,10 +520,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -543,13 +543,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>8.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -595,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -870,7 +870,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -902,16 +902,16 @@
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.4</v>
+        <v>8.2</v>
       </c>
     </row>
     <row r="6">
@@ -957,13 +957,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8">
@@ -1084,7 +1084,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5">

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -505,7 +505,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -520,10 +520,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5">
@@ -531,7 +531,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -543,13 +543,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>7.66666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -595,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>6.8</v>
+        <v>6.66666666666667</v>
       </c>
     </row>
     <row r="8">
@@ -661,7 +661,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -676,10 +676,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>8.75</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
@@ -730,7 +730,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -746,7 +746,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="8">
@@ -770,7 +770,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>
@@ -867,7 +867,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5">
@@ -893,7 +893,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
@@ -905,13 +905,13 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>8.2</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="6">
@@ -945,7 +945,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -957,13 +957,13 @@
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>6.8</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="8">
@@ -1023,7 +1023,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
@@ -1038,10 +1038,10 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>8.75</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1084,7 +1084,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1092,7 +1092,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -1108,7 +1108,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -1132,7 +1132,7 @@
         <v>16</v>
       </c>
       <c r="B10" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/frequency_in_majority.xlsx
@@ -479,7 +479,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
@@ -491,13 +491,13 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>7.83333333333333</v>
+        <v>7.57142857142857</v>
       </c>
     </row>
     <row r="4">
@@ -505,7 +505,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -517,13 +517,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4</v>
+        <v>7.16666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -557,7 +557,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -569,13 +569,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
@@ -609,7 +609,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
@@ -621,13 +621,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>6.83333333333333</v>
+        <v>6.71428571428571</v>
       </c>
     </row>
     <row r="9">
@@ -635,7 +635,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -647,13 +647,13 @@
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>7.16666666666667</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -714,7 +714,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="4">
@@ -722,7 +722,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -738,7 +738,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="7">
@@ -754,7 +754,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="9">
@@ -762,7 +762,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="10">
@@ -841,7 +841,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -853,13 +853,13 @@
         <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="4">
@@ -867,7 +867,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
@@ -879,13 +879,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4</v>
+        <v>7.17</v>
       </c>
     </row>
     <row r="5">
@@ -919,7 +919,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7">
@@ -971,7 +971,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
@@ -983,13 +983,13 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="9">
@@ -997,7 +997,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -1009,13 +1009,13 @@
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -1084,7 +1084,7 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -1100,7 +1100,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
@@ -1116,7 +1116,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1124,7 +1124,7 @@
         <v>15</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
